--- a/portfolio_collection_audit/MLC_unlinked_recordings_by_publisher.xlsx
+++ b/portfolio_collection_audit/MLC_unlinked_recordings_by_publisher.xlsx
@@ -12,14 +12,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BMG Publishing" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTM" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve Publishing" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kobalt" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raleigh Music" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reservoir" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sony Music Publishing" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Universal Music Publishing" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warner Chappell" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No publisher (label-PRO deals)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concord Publishing" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve Publishing" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kobalt" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raleigh Music" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reservoir" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPIRIT TWO (ADMIN)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sony Music Publishing" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ultra Empire Music" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Universal Music Publishing" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warner Chappell" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No publisher (label-PRO deals)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -573,865 +576,150 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BMG, Sony Music Publishing, Warner Chappell</t>
+          <t>Reservoir</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Liz Rose</t>
+          <t>Alex Cantrall</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FR6V80432397</t>
+          <t>USBGR0300053</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Catch a Falling Star</t>
+          <t>Leave (Get Out) - Radio Edit</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>JoJo</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>91855468</v>
+        <v>225194139</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C20640</t>
+          <t>L2006P</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CATCH A FALLING STAR</t>
+          <t>LEAVE (GET OUT)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>USRC15704667</t>
+          <t>FR8GV1732270</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work C20640 (CATCH A FALLING STAR) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work L2006P (LEAVE (GET OUT)) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BMG, Sony Music Publishing, Warner Chappell</t>
+          <t>Reservoir</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liz Rose</t>
+          <t>Alex Cantrall</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GBCJQ0952231</t>
+          <t>NOX9X2966702</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Catch a Falling Star (Bonus Track)</t>
+          <t>Leave (Get Out)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>Jojo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>91663018</v>
+        <v>225093733</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C20640</t>
+          <t>L2006P</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CATCH A FALLING STAR</t>
+          <t>LEAVE (GET OUT)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>USRC15704667</t>
+          <t>FR8GV1732270</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work C20640 (CATCH A FALLING STAR) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work L2006P (LEAVE (GET OUT)) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BMG, Sony Music Publishing, Warner Chappell</t>
+          <t>Reservoir</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liz Rose</t>
+          <t>Alex Cantrall</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FR6V80791801</t>
+          <t>SEYOK1625030</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Catch a Falling Star</t>
+          <t>Sorry</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Perry Como</t>
+          <t>VAPAE</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>91041456</v>
+        <v>2254742</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C20640</t>
+          <t>SVA002</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CATCH A FALLING STAR</t>
+          <t>SORRY LATINO REMIX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>USRC15704667</t>
+          <t>USUM71517619</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work C20640 (CATCH A FALLING STAR) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BMG, Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Liz Rose</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>US6XF1800338</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>It All Comes Out in the Wash</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Miranda Lambert</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>36515300</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BMG, Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Liz Rose</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GBQWS0700077</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Own Side</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Caitlin Rose</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1601326</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>USUV71903404</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Missing You</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>John Waite</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>363148457</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>USSM20100563</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>One Sweet Day</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Mariah Carey, Boyz II Men</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>272587789</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>USUV71102094</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>All I Want For Christmas Is You (SuperFestive!)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Mariah Carey, Justin Bieber</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>166224109</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ES58A1900398</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Duke of Earl - Remastered</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Gene Chandler</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>39458800</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BEZ462200003</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Forever - Remastered Kiss FM Edit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Dee Dee</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>23444741</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>F07981</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>FOREVER</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ES6091500116</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work F07981 (FOREVER) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BEZ462200006</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Forever - Remastered Instrumental Radio Edit</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Dee Dee</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>23444741</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>F07981</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>FOREVER</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ES6091500116</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work F07981 (FOREVER) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>QM4TX1936276</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Morena</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Antonia, Tom Boxer</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>19424100</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TCABW1467262</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Missing You (feat. Alison Krauss)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Alison Krauss, John Waite</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>9000141</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GBCFZ1600009</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Forever - Edit</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N-Trance</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>6974908</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>F07981</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>FOREVER</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>ES6091500116</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work F07981 (FOREVER) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Isabella Afanasieff</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>NOAJR1800041</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LOKE</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>6227392</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>H02187</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>HERO</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>USSM19303171</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work H02187 (HERO) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>K Flay</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AUNV01200037</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Hot Right Now - Radio Edit</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Rita Ora, DJ Fresh</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>89428193</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>H56265</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>HOT RIGHT NOW</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>USQX91200775</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>K Flay</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>USA561182246</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Hot Right Now (Radio Edit)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>DJ Fresh, Rita Ora</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>89428193</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>H56265</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>HOT RIGHT NOW</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>USQX91200775</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>K Flay</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>USQY51286230</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Hot Right Now</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>DJ Fresh, Rita Ora</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>89428193</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>H56265</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>HOT RIGHT NOW</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>USQX91200775</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>K Flay</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>USWBV0500007</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>High Enough</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Damn Yankees</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>84056170</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>HV9X8Q</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>HIGH ENOUGH</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>USUM71701789</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work HV9X8Q (HIGH ENOUGH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>K Flay</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>USUV72201886</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Rag Doll</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>poutyface, K.Flay</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1803658</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+          <t>Please link this ISRC to MLC work SVA002 (SORRY LATINO REMIX) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1522,1155 +810,150 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kobalt, Universal Music Publishing</t>
+          <t>Raleigh Music, SPIRIT TWO (ADMIN)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chris Styles</t>
+          <t>Kalman and Appel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USA560929214</t>
+          <t>USTB12100107</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Car Wash (Re-Recorded / Remastered Version)</t>
+          <t>Jump Around (Instrumental) - 30 Years Remaster</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rose Royce</t>
+          <t>House Of Pain</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>77298193</v>
+        <v>782439700</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C13500</t>
+          <t>J00470</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CAR WASH</t>
+          <t>JUMP AROUND (ORIGINAL VERSION)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>USMC17646466</t>
+          <t>USTB10300119</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work J00470 (JUMP AROUND (ORIGINAL VERSION)) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kobalt, Universal Music Publishing</t>
+          <t>Raleigh Music, SPIRIT TWO (ADMIN)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chris Styles</t>
+          <t>Kalman and Appel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USI4R1224216</t>
+          <t>USTB12200156</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Car Wash</t>
+          <t>Jump Around (Official Music Video) - HD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rose Royce</t>
+          <t>House Of Pain</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>52464381</v>
+        <v>731084898</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C13500</t>
+          <t>J00470</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CAR WASH</t>
+          <t>JUMP AROUND (ORIGINAL VERSION)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>USMC17646466</t>
+          <t>USTB10300119</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work J00470 (JUMP AROUND (ORIGINAL VERSION)) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kobalt, Universal Music Publishing</t>
+          <t>Raleigh Music, SPIRIT TWO (ADMIN)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chris Styles</t>
+          <t>Kalman and Appel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USA370919039</t>
+          <t>GBSMU9106953</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Carwash (Re-Recorded / Remastered)</t>
+          <t>Amigos</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rose Royce</t>
+          <t>Galvan Real</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>26078808</v>
+        <v>48424559</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AA37Y3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AMIGOS</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GBSMU9185625</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USA371570060</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Car Wash (Re-Recorded) [Remastered]</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>26078808</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>USA370935965</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Car Wash (from Car Wash) (Re-Recorded / Remastered)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>26074196</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>USMC10300494</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Car Wash - Edit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>23435375</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GBKTX0900460</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Car Wash</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>The Bubble Boys &amp; Glitter Girls</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6037305</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Adrian Belew</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>USRV82101087</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Big Energy</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Latto</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>416666211</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BB9RP3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>BIG ENERGY</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>USRC12102454</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work BB9RP3 (BIG ENERGY) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Brian kidd</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FR26V1550811</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Lemme Know</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Vince Staples</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>14794351</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LV7UK0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>LEMME KNOW</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>USUM71507707</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work LV7UK0 (LEMME KNOW) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>USIR10001261</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Rollin' (Urban Assault Vehicle)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Limp Bizkit</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1004232643</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>USIR10110286</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Let Me Blow Ya Mind - Radio Edit Video Version</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Eve</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>711118314</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Universal Music Group</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>USAE81204340</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Party Up (Up In Here)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>How High The Original Motion Picture Soundtrack, DMX</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>438828211</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GBQRF1004522</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Who Am I (What's My Name?)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Snoop Dogg</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>383643314</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BG28K1400001</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>shot me down</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Skylar Grey, David Guetta</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>299375031</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Z27038</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>SHOT ME DOWN</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>GB28K1400001</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work Z27038 (SHOT ME DOWN) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>USAT20200105</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>You Don't Love Me (No, No, No)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Dawn Penn</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>230459139</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>USSM16900805</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Thank You (Falettinme Be Mice Elf Agin)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Sly &amp; The Family Stone</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>77326767</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>USDJ20300837</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Get It On The Floor - Radio Edit</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>DMX, Swizz Beatz</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>55647542</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>SoundExchange, Universal Music Group</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>FR8GV2004710</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Grand Finale</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Method Man, Ja Rule, DMX, Nas</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>19757500</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>UK8D41401247</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>No Sunshine</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>17243130</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>USRC19606764</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Put It In Your Mouth</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Akinyele, Kia Jefferies</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>17098928</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>USJ3V0795166</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Put It In Your Mouth</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Akinyele</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>17094732</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>QM4TX1579557</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Blackout Freestyle</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Jadakiss, DMX, Sheek Louch, JAY-Z, Styles P</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>13950641</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>USDJ20300658</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Where The Hood At - Radio Edit</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>7657250</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Universal Music Group</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>DMX</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>JPD932400547</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Could You Be Loved</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Shoby, Kid On The Block</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1595793</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>C69920</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>COULD YOU BE LOVED</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>USIR28000016</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C69920 (COULD YOU BE LOVED) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Mark Hudson</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>USIV20400191</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Livin' On The Edge</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Aerosmith</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>103905132</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>L02979</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>LIVIN' ON THE EDGE</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>USIR10000445</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work L02979 (LIVIN' ON THE EDGE) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Shawn Charles</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>NL11L1800004</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Coño</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Jhorrmountain, Adje, Puri</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>179002335</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>CC8F84</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>CONO (FT. JASON DERULO)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>NLZ542001080</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work CC8F84 (CONO (FT. JASON DERULO)) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Stacy Barthe</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>USRC11400289</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Adore You Remix - Extended Mix</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Miley Cyrus, Cedric Gervais</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>23663818</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>A78671</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>ADORE YOU</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>USRC11301264</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work A78671 (ADORE YOU) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work AA37Y3 (AMIGOS) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
@@ -2685,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2981,7 +1264,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
+          <t>Sony Music Publishing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2991,21 +1274,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USUV71903404</t>
+          <t>USSM20100563</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Missing You</t>
+          <t>One Sweet Day</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>John Waite</t>
+          <t>Mariah Carey, Boyz II Men</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>363148457</v>
+        <v>272587789</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3016,7 +1299,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
+          <t>Sony Music Publishing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3026,21 +1309,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USSM20100563</t>
+          <t>USUV71102094</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>One Sweet Day</t>
+          <t>All I Want For Christmas Is You (SuperFestive!)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mariah Carey, Boyz II Men</t>
+          <t>Mariah Carey, Justin Bieber</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>272587789</v>
+        <v>166224109</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3051,7 +1334,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
+          <t>Sony Music Publishing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3061,32 +1344,47 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USUV71102094</t>
+          <t>BEZ462200003</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>All I Want For Christmas Is You (SuperFestive!)</t>
+          <t>Forever - Remastered Kiss FM Edit</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mariah Carey, Justin Bieber</t>
+          <t>Dee Dee</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>166224109</v>
+        <v>23444741</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>F07981</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FOREVER</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ES6091500116</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+          <t>Please link this ISRC to MLC work F07981 (FOREVER) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
+          <t>Sony Music Publishing</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3096,32 +1394,47 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ES58A1900398</t>
+          <t>BEZ462200006</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Duke of Earl - Remastered</t>
+          <t>Forever - Remastered Instrumental Radio Edit</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gene Chandler</t>
+          <t>Dee Dee</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>39458800</v>
+        <v>23444741</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>F07981</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>FOREVER</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ES6091500116</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+          <t>Please link this ISRC to MLC work F07981 (FOREVER) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
+          <t>Sony Music Publishing</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3131,21 +1444,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BEZ462200003</t>
+          <t>GBCFZ1600009</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Forever - Remastered Kiss FM Edit</t>
+          <t>Forever - Edit</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dee Dee</t>
+          <t>N-Trance</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>23444741</v>
+        <v>6974908</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3171,120 +1484,150 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
+          <t>Sony Music Publishing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Isabella Afanasieff</t>
+          <t>K Flay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BEZ462200006</t>
+          <t>AUNV01200037</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Forever - Remastered Instrumental Radio Edit</t>
+          <t>Hot Right Now - Radio Edit</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dee Dee</t>
+          <t>Rita Ora, DJ Fresh</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23444741</v>
+        <v>89428193</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>F07981</t>
+          <t>H56265</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FOREVER</t>
+          <t>HOT RIGHT NOW</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ES6091500116</t>
+          <t>USQX91200775</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work F07981 (FOREVER) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
+          <t>Sony Music Publishing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Isabella Afanasieff</t>
+          <t>K Flay</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>QM4TX1936276</t>
+          <t>USA561182246</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Morena</t>
+          <t>Hot Right Now (Radio Edit)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Antonia, Tom Boxer</t>
+          <t>DJ Fresh, Rita Ora</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>19424100</v>
+        <v>89428193</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>H56265</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>HOT RIGHT NOW</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>USQX91200775</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
+          <t>Sony Music Publishing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Isabella Afanasieff</t>
+          <t>K Flay</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TCABW1467262</t>
+          <t>USQY51286230</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Missing You (feat. Alison Krauss)</t>
+          <t>Hot Right Now</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alison Krauss, John Waite</t>
+          <t>DJ Fresh, Rita Ora</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9000141</v>
+        <v>89428193</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>H56265</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>HOT RIGHT NOW</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>USQX91200775</t>
+        </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
@@ -3301,40 +1644,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GBCFZ1600009</t>
+          <t>USUV71903404</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Forever - Edit</t>
+          <t>Missing You</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>N-Trance</t>
+          <t>John Waite</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6974908</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>F07981</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>FOREVER</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>ES6091500116</t>
-        </is>
+        <v>363148457</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work F07981 (FOREVER) – the original recording is already linked; this version is not.</t>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
         </is>
       </c>
     </row>
@@ -3351,40 +1679,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NOAJR1800041</t>
+          <t>ES58A1900398</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Duke of Earl - Remastered</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LOKE</t>
+          <t>Gene Chandler</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6227392</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>H02187</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>HERO</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>USSM19303171</t>
-        </is>
+        <v>39458800</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work H02187 (HERO) – the original recording is already linked; this version is not.</t>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
         </is>
       </c>
     </row>
@@ -3396,45 +1709,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>K Flay</t>
+          <t>Isabella Afanasieff</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AUNV01200037</t>
+          <t>QM4TX1936276</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hot Right Now - Radio Edit</t>
+          <t>Morena</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rita Ora, DJ Fresh</t>
+          <t>Antonia, Tom Boxer</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>89428193</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>H56265</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>HOT RIGHT NOW</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>USQX91200775</t>
-        </is>
+        <v>19424100</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
         </is>
       </c>
     </row>
@@ -3446,45 +1744,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>K Flay</t>
+          <t>Isabella Afanasieff</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA561182246</t>
+          <t>TCABW1467262</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hot Right Now (Radio Edit)</t>
+          <t>Missing You (feat. Alison Krauss)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DJ Fresh, Rita Ora</t>
+          <t>Alison Krauss, John Waite</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>89428193</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>H56265</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>HOT RIGHT NOW</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>USQX91200775</t>
-        </is>
+        <v>9000141</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
         </is>
       </c>
     </row>
@@ -3501,275 +1784,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USQY51286230</t>
+          <t>USUV72201886</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hot Right Now</t>
+          <t>Rag Doll</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DJ Fresh, Rita Ora</t>
+          <t>poutyface, K.Flay</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>89428193</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>H56265</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>HOT RIGHT NOW</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>USQX91200775</t>
-        </is>
+        <v>1803658</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work H56265 (HOT RIGHT NOW) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>K Flay</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>USWBV0500007</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>High Enough</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Damn Yankees</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>84056170</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>HV9X8Q</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>HIGH ENOUGH</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>USUM71701789</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work HV9X8Q (HIGH ENOUGH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sony Music Publishing, Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>K Flay</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>USUV72201886</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Rag Doll</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>poutyface, K.Flay</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1803658</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
           <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Ralph Jeanty</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>FR6V82452677</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Make It Home</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>August Alsina</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>31323310</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Z2412M</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>MAKE IT HOME</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>USUM71400139</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work Z2412M (MAKE IT HOME) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ralph Jeanty</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>FR6V82587895</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Benediction</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Rick Ross</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>20601367</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Z3852K</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>BENEDICTION</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>USUM71403542</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work Z3852K (BENEDICTION) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Warner Chappell</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ralph Jeanty</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>USRC11302089</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>We Just Came to Party</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>August Alsina, Kid Ink</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>6393048</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>W7704L</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>WE JUST CAME TO PARTY</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>USRC11302076</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work W7704L (WE JUST CAME TO PARTY) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
@@ -3779,6 +1812,1793 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="95" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>isrc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recording_title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>artist</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>spotify_plays</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_mlc_work_id</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_work_title</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>isrc_already_linked_to_that_work</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>label_paying_this_isrc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Curve Publishing, Ultra Empire Music</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Allie Crystal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GX89G2284771</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>snap (slowed + reverb)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>slowed and reverbed tunes, Melodyz Town, eyeroze</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1365741</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SH0NMA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>USSM12207342</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work SH0NMA (SNAP) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="95" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>isrc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recording_title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>artist</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>spotify_plays</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_mlc_work_id</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_work_title</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>isrc_already_linked_to_that_work</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>label_paying_this_isrc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Concord Publishing, Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mark Hudson</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>USIV20400191</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Livin' On The Edge</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Aerosmith</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>103905132</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>L02979</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LIVIN' ON THE EDGE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>USIR10000445</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work L02979 (LIVIN' ON THE EDGE) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Kobalt, Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chris Styles</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>USA370919039</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Carwash (Re-Recorded / Remastered)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Rose Royce</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>26078808</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Adrian Belew</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>USRV82101087</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Big Energy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Latto</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>416666211</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BB9RP3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>BIG ENERGY</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>USRC12102454</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work BB9RP3 (BIG ENERGY) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brian kidd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FR26V1550811</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lemme Know</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vince Staples</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>14794351</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LV7UK0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LEMME KNOW</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>USUM71507707</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work LV7UK0 (LEMME KNOW) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>USIR10001261</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rollin' (Urban Assault Vehicle)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Limp Bizkit</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1004232643</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USIR10110286</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Let Me Blow Ya Mind - Radio Edit Video Version</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>711118314</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Universal Music Group</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USAE81204340</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Party Up (Up In Here)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>How High The Original Motion Picture Soundtrack, DMX</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>438828211</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GBQRF1004522</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Who Am I (What's My Name?)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Snoop Dogg</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>383643314</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BG28K1400001</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>shot me down</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Skylar Grey, David Guetta</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>299375031</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Z27038</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SHOT ME DOWN</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>GB28K1400001</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work Z27038 (SHOT ME DOWN) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>USAT20200105</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>You Don't Love Me (No, No, No)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dawn Penn</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>230459139</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>USSM16900805</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Thank You (Falettinme Be Mice Elf Agin)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sly &amp; The Family Stone</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>77326767</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>USDJ20300837</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Get It On The Floor - Radio Edit</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DMX, Swizz Beatz</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>55647542</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SoundExchange, Universal Music Group</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FR8GV2004710</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Grand Finale</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Method Man, Ja Rule, DMX, Nas</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>19757500</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>UK8D41401247</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No Sunshine</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>17243130</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USRC19606764</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Put It In Your Mouth</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Akinyele, Kia Jefferies</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>17098928</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>USJ3V0795166</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Put It In Your Mouth</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Akinyele</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>17094732</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>QM4TX1579557</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Blackout Freestyle</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Jadakiss, DMX, Sheek Louch, JAY-Z, Styles P</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>13950641</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>USDJ20300658</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Where The Hood At - Radio Edit</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>7657250</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Universal Music Group</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>JPD932400547</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Could You Be Loved</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Shoby, Kid On The Block</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1595793</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>C69920</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>COULD YOU BE LOVED</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>USIR28000016</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work C69920 (COULD YOU BE LOVED) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Shawn Charles</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NL11L1800004</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Coño</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Jhorrmountain, Adje, Puri</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>179002335</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CC8F84</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CONO (FT. JASON DERULO)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NLZ542001080</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work CC8F84 (CONO (FT. JASON DERULO)) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Universal Music Publishing</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Stacy Barthe</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>USRC11400289</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Adore You Remix - Extended Mix</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Miley Cyrus, Cedric Gervais</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>23663818</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="95" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>isrc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recording_title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>artist</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>spotify_plays</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_mlc_work_id</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>suggested_work_title</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>isrc_already_linked_to_that_work</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>label_paying_this_isrc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BMG, Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Liz Rose</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FR6V80432397</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Catch a Falling Star</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Perry Como</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>91855468</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>C20640</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CATCH A FALLING STAR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>USRC15704667</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work C20640 (CATCH A FALLING STAR) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BMG, Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Liz Rose</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GBCJQ0952231</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Catch a Falling Star (Bonus Track)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Perry Como</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>91663018</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C20640</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CATCH A FALLING STAR</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>USRC15704667</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work C20640 (CATCH A FALLING STAR) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BMG, Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Liz Rose</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FR6V80791801</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Catch a Falling Star</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Perry Como</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>91041456</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C20640</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CATCH A FALLING STAR</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>USRC15704667</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work C20640 (CATCH A FALLING STAR) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BMG, Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Liz Rose</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>US6XF1800338</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>It All Comes Out in the Wash</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Miranda Lambert</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>36515300</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BMG, Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Liz Rose</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GBQWS0700077</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Own Side</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Caitlin Rose</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1601326</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Isabella Afanasieff</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USUV71903404</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Missing You</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>John Waite</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>363148457</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Isabella Afanasieff</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ES58A1900398</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Duke of Earl - Remastered</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Gene Chandler</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>39458800</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Isabella Afanasieff</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>QM4TX1936276</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Morena</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Antonia, Tom Boxer</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>19424100</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Isabella Afanasieff</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TCABW1467262</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Missing You (feat. Alison Krauss)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Alison Krauss, John Waite</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>9000141</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sony Music Publishing, Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>K Flay</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>USUV72201886</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rag Doll</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>poutyface, K.Flay</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1803658</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Isabella Afanasieff</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NOAJR1800041</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LOKE</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6227392</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>H02187</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>HERO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>USSM19303171</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work H02187 (HERO) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>K Flay</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>USWBV0500007</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>High Enough</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Damn Yankees</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>84056170</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HV9X8Q</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>HIGH ENOUGH</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>USUM71701789</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work HV9X8Q (HIGH ENOUGH) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ralph Jeanty</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FR6V82452677</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Make It Home</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>August Alsina</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>31323310</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Z2412M</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>MAKE IT HOME</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>USUM71400139</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work Z2412M (MAKE IT HOME) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ralph Jeanty</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FR6V82587895</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Benediction</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Rick Ross</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>20601367</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Z3852K</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BENEDICTION</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>USUM71403542</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work Z3852K (BENEDICTION) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Warner Chappell</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ralph Jeanty</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USRC11302089</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>We Just Came to Party</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>August Alsina, Kid Ink</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>6393048</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>W7704L</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>WE JUST CAME TO PARTY</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>USRC11302076</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work W7704L (WE JUST CAME TO PARTY) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4888,7 +4708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4932,7 +4752,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4940,10 +4760,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4270527848</v>
+        <v>4059139590</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -4953,7 +4773,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4961,41 +4781,41 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1763380384</v>
+        <v>1738190839</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Warner Chappell</t>
+          <t>Raleigh Music</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Isabella Afanasieff, K Flay, Liz Rose, Ralph Jeanty</t>
+          <t>Kalman and Appel</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1655073878</v>
+        <v>1610077805</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>SPIRIT TWO (ADMIN)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5003,10 +4823,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1610077805</v>
+        <v>1561949157</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5016,7 +4836,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5024,100 +4844,100 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1596756153</v>
+        <v>1506472591</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BMG</t>
+          <t>Warner Chappell</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Liz Rose, Rebel Made, Vinyl Crown</t>
+          <t>Isabella Afanasieff, K Flay, Liz Rose, Ralph Jeanty</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>483335279</v>
+        <v>894113011</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reservoir</t>
+          <t>BMG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alex Cantrall</t>
+          <t>Liz Rose, Rebel Made, Vinyl Crown</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>452542614</v>
+        <v>483335279</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CTM</t>
+          <t>Reservoir</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mike and Keys</t>
+          <t>Alex Cantrall</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>234693204</v>
+        <v>452542614</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BMG Publishing</t>
+          <t>CTM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vinyl Crown</t>
+          <t>Mike and Keys</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3688598</v>
+        <v>234693204</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Curve Publishing</t>
+          <t>Concord Publishing</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5125,13 +4945,76 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Mark Hudson</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>103905132</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BMG Publishing</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Vinyl Crown</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3688598</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Curve Publishing</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Allie Crystal</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>1365741</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ultra Empire Music</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Allie Crystal</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1365741</v>
+      </c>
+      <c r="E14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5222,85 +5105,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BMG, BMG Publishing</t>
+          <t>BMG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vinyl Crown</t>
+          <t>Rebel Made</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FR6V81954899</t>
+          <t>GB0200202003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>I'm a G (Bury Me a G) [Explicit]</t>
+          <t>Invisible</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kidd Kidd</t>
+          <t>Alison Moyet</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3688598</v>
+        <v>25189545</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IV7HAL</t>
+          <t>I79190</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>I'M A G (BURY ME A G)</t>
+          <t>INVISIBLE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>QZZ7X2539540</t>
+          <t>GBARL0901099</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work IV7HAL (I'M A G (BURY ME A G)) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work I79190 (INVISIBLE) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BMG, Kobalt</t>
+          <t>BMG, BMG Publishing</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rebel Made</t>
+          <t>Vinyl Crown</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USRV81200549</t>
+          <t>FR6V81954899</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Long Live A$AP</t>
+          <t>I'm a G (Bury Me a G) [Explicit]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A$AP Rocky</t>
+          <t>Kidd Kidd</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>120683336</v>
+        <v>3688598</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>IV7HAL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>I'M A G (BURY ME A G)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>QZZ7X2539540</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+          <t>Please link this ISRC to MLC work IV7HAL (I'M A G (BURY ME A G)) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
@@ -5317,40 +5215,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GB0200202003</t>
+          <t>USRV81200549</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Invisible</t>
+          <t>Long Live A$AP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alison Moyet</t>
+          <t>A$AP Rocky</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25189545</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>I79190</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>INVISIBLE</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>GBARL0901099</t>
-        </is>
+        <v>120683336</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work I79190 (INVISIBLE) – the original recording is already linked; this version is not.</t>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
         </is>
       </c>
     </row>
@@ -6199,50 +6082,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Curve Publishing</t>
+          <t>Concord Publishing, Universal Music Publishing</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Allie Crystal</t>
+          <t>Mark Hudson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GX89G2284771</t>
+          <t>USIV20400191</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>snap (slowed + reverb)</t>
+          <t>Livin' On The Edge</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>slowed and reverbed tunes, Melodyz Town, eyeroze</t>
+          <t>Aerosmith</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1365741</v>
+        <v>103905132</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SH0NMA</t>
+          <t>L02979</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>LIVIN' ON THE EDGE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>USSM12207342</t>
+          <t>USIR10000445</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work SH0NMA (SNAP) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work L02979 (LIVIN' ON THE EDGE) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6333,570 +6216,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BMG, Kobalt</t>
+          <t>Curve Publishing, Ultra Empire Music</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rebel Made</t>
+          <t>Allie Crystal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USRV81200549</t>
+          <t>GX89G2284771</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Long Live A$AP</t>
+          <t>snap (slowed + reverb)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A$AP Rocky</t>
+          <t>slowed and reverbed tunes, Melodyz Town, eyeroze</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>120683336</v>
+        <v>1365741</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SH0NMA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>USSM12207342</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BMG, Kobalt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rebel Made</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GB0200202003</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Invisible</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Alison Moyet</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>25189545</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>I79190</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>INVISIBLE</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>GBARL0901099</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work I79190 (INVISIBLE) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BMG, Kobalt</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rebel Made</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>QZWDW2304430</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>In the End (Extended Mix) [with Fleurie]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>DJ Dark, Fleurie</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>21097232</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>E3100T</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>THE END</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>GB5KW1803055</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work E3100T (THE END) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Kobalt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jacob Schulze</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USLIC0600478</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bye Bye Bye</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>*NSYNC</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1340569426</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>B15451</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>BYE BYE BYE</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>USJI10000001</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work B15451 (BYE BYE BYE) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Kobalt</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Jacob Schulze</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>USGF19822008</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Slam Dunk (Da Funk)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Five</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>18373779</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>S28416</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SLAM DUNK DA FUNK</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>GBARL9700384</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work S28416 (SLAM DUNK DA FUNK) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>USA560929214</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Car Wash (Re-Recorded / Remastered Version)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>77298193</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>USI4R1224216</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Car Wash</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>52464381</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>USA370919039</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Carwash (Re-Recorded / Remastered)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>26078808</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>USA371570060</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Car Wash (Re-Recorded) [Remastered]</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>26078808</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>USA370935965</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Car Wash (from Car Wash) (Re-Recorded / Remastered)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>26074196</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>USMC10300494</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Car Wash - Edit</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Rose Royce</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>23435375</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Kobalt, Universal Music Publishing</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Chris Styles</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GBKTX0900460</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Car Wash</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>The Bubble Boys &amp; Glitter Girls</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>6037305</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>C13500</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>CAR WASH</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>USMC17646466</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work SH0NMA (SNAP) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
@@ -6987,516 +6350,516 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>BMG, Kobalt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Rebel Made</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USTB12100107</t>
+          <t>USRV81200549</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jump Around (Instrumental) - 30 Years Remaster</t>
+          <t>Long Live A$AP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>House Of Pain</t>
+          <t>A$AP Rocky</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>782439700</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>J00470</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>JUMP AROUND (ORIGINAL VERSION)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>USTB10300119</t>
-        </is>
+        <v>120683336</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work J00470 (JUMP AROUND (ORIGINAL VERSION)) – the original recording is already linked; this version is not.</t>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>BMG, Kobalt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Rebel Made</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>USTB12200156</t>
+          <t>QZWDW2304430</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jump Around (Official Music Video) - HD</t>
+          <t>In the End (Extended Mix) [with Fleurie]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>House Of Pain</t>
+          <t>DJ Dark, Fleurie</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>731084898</v>
+        <v>21097232</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>J00470</t>
+          <t>E3100T</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>JUMP AROUND (ORIGINAL VERSION)</t>
+          <t>THE END</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>USTB10300119</t>
+          <t>GB5KW1803055</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work J00470 (JUMP AROUND (ORIGINAL VERSION)) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work E3100T (THE END) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Chris Styles</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GBSMU9106953</t>
+          <t>USA560929214</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amigos</t>
+          <t>Car Wash (Re-Recorded / Remastered Version)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galvan Real</t>
+          <t>Rose Royce</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>48424559</v>
+        <v>77298193</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AA37Y3</t>
+          <t>C13500</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AMIGOS</t>
+          <t>CAR WASH</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GBSMU9185625</t>
+          <t>USMC17646466</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work AA37Y3 (AMIGOS) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Chris Styles</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FR0O70828815</t>
+          <t>USI4R1224216</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Side By Side</t>
+          <t>Car Wash</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kay Starr</t>
+          <t>Rose Royce</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7073286</v>
+        <v>52464381</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>S28210</t>
+          <t>C13500</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SIDE BY SIDE</t>
+          <t>CAR WASH</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>USCA29100360</t>
+          <t>USMC17646466</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Chris Styles</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GBELT0815600</t>
+          <t>USA371570060</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Side By Side</t>
+          <t>Car Wash (Re-Recorded) [Remastered]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hal Mooney, Kay Starr</t>
+          <t>Rose Royce</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7071612</v>
+        <v>26078808</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>S28210</t>
+          <t>C13500</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SIDE BY SIDE</t>
+          <t>CAR WASH</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>USCA29100360</t>
+          <t>USMC17646466</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Chris Styles</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GBELT0808293</t>
+          <t>USA370935965</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Side By Side</t>
+          <t>Car Wash (from Car Wash) (Re-Recorded / Remastered)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kay Starr, Hal Mooney Orchestra</t>
+          <t>Rose Royce</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7069799</v>
+        <v>26074196</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>S28210</t>
+          <t>C13500</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SIDE BY SIDE</t>
+          <t>CAR WASH</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>USCA29100360</t>
+          <t>USMC17646466</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Chris Styles</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GBCJQ8801390</t>
+          <t>USMC10300494</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Side By Side</t>
+          <t>Car Wash - Edit</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kay Starr</t>
+          <t>Rose Royce</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7067909</v>
+        <v>23435375</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>S28210</t>
+          <t>C13500</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SIDE BY SIDE</t>
+          <t>CAR WASH</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>USCA29100360</t>
+          <t>USMC17646466</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Chris Styles</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GBGN32309503</t>
+          <t>GBKTX0900460</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Side by Side (Remastered 2014)</t>
+          <t>Car Wash</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kay Starr</t>
+          <t>The Bubble Boys &amp; Glitter Girls</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7030326</v>
+        <v>6037305</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>S28210</t>
+          <t>C13500</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SIDE BY SIDE</t>
+          <t>CAR WASH</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>USCA29100360</t>
+          <t>USMC17646466</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work C13500 (CAR WASH) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Jacob Schulze</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USESK0607658</t>
+          <t>USLIC0600478</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Wah Watusi</t>
+          <t>Bye Bye Bye</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Orlons</t>
+          <t>*NSYNC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5613285</v>
+        <v>1340569426</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>W00752</t>
+          <t>B15451</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>WAH-WATUSI</t>
+          <t>BYE BYE BYE</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>USA176240600</t>
+          <t>USJI10000001</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work W00752 (WAH-WATUSI) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work B15451 (BYE BYE BYE) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Jacob Schulze</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FR6V80142772</t>
+          <t>USGF19822008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wah Watusi</t>
+          <t>Slam Dunk (Da Funk)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlons</t>
+          <t>Five</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5611465</v>
+        <v>18373779</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S28416</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SLAM DUNK DA FUNK</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>GBARL9700384</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+          <t>Please link this ISRC to MLC work S28416 (SLAM DUNK DA FUNK) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raleigh Music</t>
+          <t>Kobalt, Universal Music Publishing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kalman and Appel</t>
+          <t>Chris Styles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEXO52486822</t>
+          <t>USA370919039</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Fabulous</t>
+          <t>Carwash (Re-Recorded / Remastered)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Charlie Gracie</t>
+          <t>Rose Royce</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1590966</v>
+        <v>26078808</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -7515,7 +6878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7591,150 +6954,520 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Reservoir</t>
+          <t>Raleigh Music</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alex Cantrall</t>
+          <t>Kalman and Appel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>USBGR0300053</t>
+          <t>FR0O70828815</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Leave (Get Out) - Radio Edit</t>
+          <t>Side By Side</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JoJo</t>
+          <t>Kay Starr</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>225194139</v>
+        <v>7073286</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>L2006P</t>
+          <t>S28210</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LEAVE (GET OUT)</t>
+          <t>SIDE BY SIDE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FR8GV1732270</t>
+          <t>USCA29100360</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work L2006P (LEAVE (GET OUT)) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reservoir</t>
+          <t>Raleigh Music</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alex Cantrall</t>
+          <t>Kalman and Appel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NOX9X2966702</t>
+          <t>GBELT0815600</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Leave (Get Out)</t>
+          <t>Side By Side</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jojo</t>
+          <t>Hal Mooney, Kay Starr</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>225093733</v>
+        <v>7071612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>L2006P</t>
+          <t>S28210</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>LEAVE (GET OUT)</t>
+          <t>SIDE BY SIDE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FR8GV1732270</t>
+          <t>USCA29100360</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work L2006P (LEAVE (GET OUT)) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reservoir</t>
+          <t>Raleigh Music</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alex Cantrall</t>
+          <t>Kalman and Appel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEYOK1625030</t>
+          <t>GBELT0808293</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sorry</t>
+          <t>Side By Side</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VAPAE</t>
+          <t>Kay Starr, Hal Mooney Orchestra</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2254742</v>
+        <v>7069799</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SVA002</t>
+          <t>S28210</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SORRY LATINO REMIX</t>
+          <t>SIDE BY SIDE</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>USUM71517619</t>
+          <t>USCA29100360</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Please link this ISRC to MLC work SVA002 (SORRY LATINO REMIX) – the original recording is already linked; this version is not.</t>
+          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Raleigh Music</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kalman and Appel</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GBCJQ8801390</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Side By Side</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kay Starr</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>7067909</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>S28210</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SIDE BY SIDE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>USCA29100360</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Raleigh Music</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kalman and Appel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GBGN32309503</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Side by Side (Remastered 2014)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kay Starr</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>7030326</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S28210</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SIDE BY SIDE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>USCA29100360</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work S28210 (SIDE BY SIDE) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Raleigh Music</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kalman and Appel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USESK0607658</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Wah Watusi</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>The Orlons</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5613285</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>W00752</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>WAH-WATUSI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>USA176240600</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work W00752 (WAH-WATUSI) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Raleigh Music</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kalman and Appel</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FR6V80142772</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Wah Watusi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Orlons</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5611465</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Raleigh Music</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kalman and Appel</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEXO52486822</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fabulous</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Charlie Gracie</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1590966</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Please match this ISRC to the correct MLC work for our composition and confirm the claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Raleigh Music, SPIRIT TWO (ADMIN)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kalman and Appel</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>USTB12100107</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jump Around (Instrumental) - 30 Years Remaster</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>House Of Pain</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>782439700</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>J00470</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>JUMP AROUND (ORIGINAL VERSION)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>USTB10300119</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work J00470 (JUMP AROUND (ORIGINAL VERSION)) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Raleigh Music, SPIRIT TWO (ADMIN)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kalman and Appel</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>USTB12200156</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Jump Around (Official Music Video) - HD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>House Of Pain</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>731084898</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>J00470</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>JUMP AROUND (ORIGINAL VERSION)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>USTB10300119</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work J00470 (JUMP AROUND (ORIGINAL VERSION)) – the original recording is already linked; this version is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Raleigh Music, SPIRIT TWO (ADMIN)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kalman and Appel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GBSMU9106953</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Amigos</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Galvan Real</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>48424559</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AA37Y3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AMIGOS</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GBSMU9185625</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Please link this ISRC to MLC work AA37Y3 (AMIGOS) – the original recording is already linked; this version is not.</t>
         </is>
       </c>
     </row>
